--- a/master/result/109_穿越称帝_婉清的王朝/109_穿越称帝_婉清的王朝.xlsx
+++ b/master/result/109_穿越称帝_婉清的王朝/109_穿越称帝_婉清的王朝.xlsx
@@ -397,577 +397,731 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:D51"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文含义</v>
+        <v>词性</v>
+      </c>
+      <c r="D1" t="str">
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>sometime</v>
       </c>
       <c r="B2" t="str">
-        <v>sometime</v>
+        <v>/sometime/</v>
       </c>
       <c r="C2" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>某个时候</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>furniture</v>
       </c>
       <c r="B3" t="str">
-        <v>furniture</v>
+        <v>/furniture/</v>
       </c>
       <c r="C3" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>家具</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>queen</v>
       </c>
       <c r="B4" t="str">
-        <v>queen</v>
+        <v>/queen/</v>
       </c>
       <c r="C4" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D4" t="str">
         <v>女王</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>paragraph</v>
       </c>
       <c r="B5" t="str">
-        <v>paragraph</v>
+        <v>/paragraph/</v>
       </c>
       <c r="C5" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D5" t="str">
         <v>段落</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>obstruction</v>
       </c>
       <c r="B6" t="str">
-        <v>obstruction</v>
+        <v>/obstruction/</v>
       </c>
       <c r="C6" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D6" t="str">
         <v>障碍</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>elevator</v>
       </c>
       <c r="B7" t="str">
-        <v>elevator</v>
+        <v>/elevator/</v>
       </c>
       <c r="C7" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D7" t="str">
         <v>电梯</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>practically</v>
       </c>
       <c r="B8" t="str">
-        <v>practically</v>
+        <v>/practically/</v>
       </c>
       <c r="C8" t="str">
+        <v>adv.</v>
+      </c>
+      <c r="D8" t="str">
         <v>几乎</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>eliminate</v>
       </c>
       <c r="B9" t="str">
-        <v>eliminate</v>
+        <v>/ɪˈlɪmɪneɪt/</v>
       </c>
       <c r="C9" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D9" t="str">
         <v>消除</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>orchard</v>
       </c>
       <c r="B10" t="str">
-        <v>orchard</v>
+        <v>/orchard/</v>
       </c>
       <c r="C10" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D10" t="str">
         <v>果园</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>less</v>
       </c>
       <c r="B11" t="str">
-        <v>less</v>
+        <v>/less/</v>
       </c>
       <c r="C11" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D11" t="str">
         <v>更少</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>ministry</v>
       </c>
       <c r="B12" t="str">
-        <v>ministry</v>
+        <v>/ministry/</v>
       </c>
       <c r="C12" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D12" t="str">
         <v>部</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>engineering</v>
       </c>
       <c r="B13" t="str">
-        <v>engineering</v>
+        <v>/engineering/</v>
       </c>
       <c r="C13" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D13" t="str">
         <v>工程学</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>state</v>
       </c>
       <c r="B14" t="str">
-        <v>state</v>
+        <v>/state/</v>
       </c>
       <c r="C14" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D14" t="str">
         <v>状态</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>stranger</v>
       </c>
       <c r="B15" t="str">
-        <v>stranger</v>
+        <v>/stranger/</v>
       </c>
       <c r="C15" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D15" t="str">
         <v>陌生人</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>poster</v>
       </c>
       <c r="B16" t="str">
-        <v>poster</v>
+        <v>/poster/</v>
       </c>
       <c r="C16" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D16" t="str">
         <v>海报</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>discard</v>
       </c>
       <c r="B17" t="str">
-        <v>discard</v>
+        <v>/discard/</v>
       </c>
       <c r="C17" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D17" t="str">
         <v>丢弃</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>census</v>
       </c>
       <c r="B18" t="str">
-        <v>census</v>
+        <v>/census/</v>
       </c>
       <c r="C18" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D18" t="str">
         <v>人口普查</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>marital</v>
       </c>
       <c r="B19" t="str">
-        <v>marital</v>
+        <v>/marital/</v>
       </c>
       <c r="C19" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D19" t="str">
         <v>婚姻的</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>cow</v>
       </c>
       <c r="B20" t="str">
-        <v>cow</v>
+        <v>/kaʊ/</v>
       </c>
       <c r="C20" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D20" t="str">
         <v>母牛</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>ditch</v>
       </c>
       <c r="B21" t="str">
-        <v>ditch</v>
+        <v>/ditch/</v>
       </c>
       <c r="C21" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D21" t="str">
         <v>沟渠</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>selection</v>
       </c>
       <c r="B22" t="str">
-        <v>selection</v>
+        <v>/selection/</v>
       </c>
       <c r="C22" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D22" t="str">
         <v>选择</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>packet</v>
       </c>
       <c r="B23" t="str">
-        <v>packet</v>
+        <v>/packet/</v>
       </c>
       <c r="C23" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D23" t="str">
         <v>小包裹</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>device</v>
       </c>
       <c r="B24" t="str">
-        <v>device</v>
+        <v>/device/</v>
       </c>
       <c r="C24" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D24" t="str">
         <v>装置</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>chancellor</v>
       </c>
       <c r="B25" t="str">
-        <v>chancellor</v>
+        <v>/chancellor/</v>
       </c>
       <c r="C25" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D25" t="str">
         <v>大臣</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>book</v>
       </c>
       <c r="B26" t="str">
-        <v>book</v>
+        <v>/bʊk/</v>
       </c>
       <c r="C26" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D26" t="str">
         <v>书</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>liberty</v>
       </c>
       <c r="B27" t="str">
-        <v>liberty</v>
+        <v>/liberty/</v>
       </c>
       <c r="C27" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D27" t="str">
         <v>自由</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>president</v>
       </c>
       <c r="B28" t="str">
-        <v>president</v>
+        <v>/president/</v>
       </c>
       <c r="C28" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D28" t="str">
         <v>总统</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>bubble</v>
       </c>
       <c r="B29" t="str">
-        <v>bubble</v>
+        <v>/ˈbʌbəl/</v>
       </c>
       <c r="C29" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D29" t="str">
         <v>泡泡</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>decline</v>
       </c>
       <c r="B30" t="str">
-        <v>decline</v>
+        <v>/dɪˈklaɪn/</v>
       </c>
       <c r="C30" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D30" t="str">
         <v>下降</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>bargain</v>
       </c>
       <c r="B31" t="str">
-        <v>bargain</v>
+        <v>/bargain/</v>
       </c>
       <c r="C31" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D31" t="str">
         <v>讨价还价</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>photo</v>
       </c>
       <c r="B32" t="str">
-        <v>photo</v>
+        <v>/photo/</v>
       </c>
       <c r="C32" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D32" t="str">
         <v>照片</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>robust</v>
       </c>
       <c r="B33" t="str">
-        <v>robust</v>
+        <v>/robust/</v>
       </c>
       <c r="C33" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D33" t="str">
         <v>强健的</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>instance</v>
       </c>
       <c r="B34" t="str">
-        <v>instance</v>
+        <v>/instance/</v>
       </c>
       <c r="C34" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D34" t="str">
         <v>例子</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>ash</v>
       </c>
       <c r="B35" t="str">
-        <v>ash</v>
+        <v>/ash/</v>
       </c>
       <c r="C35" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D35" t="str">
         <v>灰</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>elaborate</v>
       </c>
       <c r="B36" t="str">
-        <v>elaborate</v>
+        <v>/elaborate/</v>
       </c>
       <c r="C36" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D36" t="str">
         <v>精心制作的</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>hay</v>
       </c>
       <c r="B37" t="str">
-        <v>hay</v>
+        <v>/hay/</v>
       </c>
       <c r="C37" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D37" t="str">
         <v>干草</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>infectious</v>
       </c>
       <c r="B38" t="str">
+        <v>/infectious/</v>
+      </c>
+      <c r="C38" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D38" t="str">
+        <v>传染的</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>key</v>
+      </c>
+      <c r="B39" t="str">
+        <v>/key/</v>
+      </c>
+      <c r="C39" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D39" t="str">
+        <v>钥匙</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>legacy</v>
+      </c>
+      <c r="B40" t="str">
+        <v>/legacy/</v>
+      </c>
+      <c r="C40" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D40" t="str">
+        <v>遗产</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>near</v>
+      </c>
+      <c r="B41" t="str">
+        <v>/near/</v>
+      </c>
+      <c r="C41" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D41" t="str">
+        <v>靠近</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>against</v>
+      </c>
+      <c r="B42" t="str">
+        <v>/against/</v>
+      </c>
+      <c r="C42" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D42" t="str">
+        <v>对抗</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>company</v>
+      </c>
+      <c r="B43" t="str">
+        <v>/company/</v>
+      </c>
+      <c r="C43" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D43" t="str">
+        <v>公司</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>mate</v>
+      </c>
+      <c r="B44" t="str">
+        <v>/mate/</v>
+      </c>
+      <c r="C44" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D44" t="str">
+        <v>伙伴</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>hammer</v>
+      </c>
+      <c r="B45" t="str">
+        <v>/hammer/</v>
+      </c>
+      <c r="C45" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D45" t="str">
+        <v>锤子</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>sneak</v>
+      </c>
+      <c r="B46" t="str">
+        <v>/sneak/</v>
+      </c>
+      <c r="C46" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D46" t="str">
+        <v>潜行</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>applaud</v>
+      </c>
+      <c r="B47" t="str">
+        <v>/applaud/</v>
+      </c>
+      <c r="C47" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D47" t="str">
+        <v>鼓掌</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>divine</v>
+      </c>
+      <c r="B48" t="str">
+        <v>/divine/</v>
+      </c>
+      <c r="C48" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D48" t="str">
+        <v>神圣的</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
         <v>infectious</v>
       </c>
-      <c r="C38" t="str">
-        <v>传染的</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39">
-        <v>38</v>
-      </c>
-      <c r="B39" t="str">
-        <v>key</v>
-      </c>
-      <c r="C39" t="str">
-        <v>钥匙</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40">
-        <v>39</v>
-      </c>
-      <c r="B40" t="str">
-        <v>legacy</v>
-      </c>
-      <c r="C40" t="str">
-        <v>遗产</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41">
-        <v>40</v>
-      </c>
-      <c r="B41" t="str">
-        <v>near</v>
-      </c>
-      <c r="C41" t="str">
-        <v>靠近</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42">
-        <v>41</v>
-      </c>
-      <c r="B42" t="str">
-        <v>against</v>
-      </c>
-      <c r="C42" t="str">
-        <v>对抗</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43">
-        <v>42</v>
-      </c>
-      <c r="B43" t="str">
-        <v>company</v>
-      </c>
-      <c r="C43" t="str">
-        <v>公司</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44">
-        <v>43</v>
-      </c>
-      <c r="B44" t="str">
-        <v>mate</v>
-      </c>
-      <c r="C44" t="str">
-        <v>伙伴</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45">
-        <v>44</v>
-      </c>
-      <c r="B45" t="str">
-        <v>hammer</v>
-      </c>
-      <c r="C45" t="str">
-        <v>锤子</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46">
-        <v>45</v>
-      </c>
-      <c r="B46" t="str">
-        <v>sneak</v>
-      </c>
-      <c r="C46" t="str">
-        <v>潜行</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47">
-        <v>46</v>
-      </c>
-      <c r="B47" t="str">
-        <v>applaud</v>
-      </c>
-      <c r="C47" t="str">
-        <v>鼓掌</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48">
-        <v>47</v>
-      </c>
-      <c r="B48" t="str">
-        <v>divine</v>
-      </c>
-      <c r="C48" t="str">
-        <v>神圣的</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49">
-        <v>48</v>
-      </c>
       <c r="B49" t="str">
-        <v>infectious</v>
+        <v>/infectious/</v>
       </c>
       <c r="C49" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D49" t="str">
         <v>有感染力的</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
+      <c r="A50" t="str">
+        <v>forth</v>
       </c>
       <c r="B50" t="str">
-        <v>forth</v>
+        <v>/forth/</v>
       </c>
       <c r="C50" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D50" t="str">
         <v>向前</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51">
-        <v>50</v>
+      <c r="A51" t="str">
+        <v>below</v>
       </c>
       <c r="B51" t="str">
-        <v>below</v>
+        <v>/below/</v>
       </c>
       <c r="C51" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D51" t="str">
         <v>在...下面</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D51"/>
   </ignoredErrors>
 </worksheet>
 </file>